--- a/output/yearly_benthic_cover_iteration_99_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_99_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.37538651671086</v>
+        <v>45.37568888395052</v>
       </c>
       <c r="M2" t="n">
-        <v>99.42048458844187</v>
+        <v>99.6434918508721</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08820140119907</v>
+        <v>88.01865439383022</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95662681737394</v>
+        <v>45.93980913831557</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228865540652277</v>
+        <v>2.228699973742813</v>
       </c>
       <c r="E3" t="n">
-        <v>5.725635380188089</v>
+        <v>5.712165949511832</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429551802174257</v>
+        <v>0.7428999912476044</v>
       </c>
       <c r="G3" t="n">
-        <v>33.982186348051</v>
+        <v>33.97708884396182</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17593829000158</v>
+        <v>34.1733995973898</v>
       </c>
       <c r="I3" t="n">
-        <v>6.589150785729783</v>
+        <v>6.541275092678821</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64346987635891</v>
+        <v>4.643124945297528</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91179859880095</v>
+        <v>11.98134560616979</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89507217789527</v>
+        <v>48.84404379565932</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7634975940701</v>
+        <v>106.7651985401447</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.23302009497058</v>
+        <v>87.06821152440783</v>
       </c>
       <c r="C4" t="n">
-        <v>42.7396209742317</v>
+        <v>42.61892231858042</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188004932200938</v>
+        <v>2.182721795669168</v>
       </c>
       <c r="E4" t="n">
-        <v>6.537754400382856</v>
+        <v>6.504734074797008</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445173234228309</v>
+        <v>0.7444535866089886</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35920896993522</v>
+        <v>33.27614001294073</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24779687745023</v>
+        <v>34.24486498401348</v>
       </c>
       <c r="I4" t="n">
-        <v>5.502504320185818</v>
+        <v>5.462462154072272</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653233271392693</v>
+        <v>4.652834916306179</v>
       </c>
       <c r="K4" t="n">
-        <v>12.7669799050294</v>
+        <v>12.93178847559217</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31036715446865</v>
+        <v>44.26758711991968</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81696803372975</v>
+        <v>99.81829791409227</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.0741314246434</v>
+        <v>85.90071729651065</v>
       </c>
       <c r="C5" t="n">
-        <v>42.43483366675156</v>
+        <v>42.29923054129543</v>
       </c>
       <c r="D5" t="n">
-        <v>2.131539216190308</v>
+        <v>2.125749916294192</v>
       </c>
       <c r="E5" t="n">
-        <v>7.13463118221318</v>
+        <v>7.09496984534041</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458417623595011</v>
+        <v>0.7457709166409296</v>
       </c>
       <c r="G5" t="n">
-        <v>32.4983098045294</v>
+        <v>32.40758945434749</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30872106853705</v>
+        <v>34.30546216548277</v>
       </c>
       <c r="I5" t="n">
-        <v>4.593577376067079</v>
+        <v>4.560106769399054</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661511014746881</v>
+        <v>4.66106822900581</v>
       </c>
       <c r="K5" t="n">
-        <v>13.92586857535661</v>
+        <v>14.09928270348933</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48645041566444</v>
+        <v>43.44975169537989</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8471526577726</v>
+        <v>99.84826494016465</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.77119445089036</v>
+        <v>84.533399958347</v>
       </c>
       <c r="C6" t="n">
-        <v>41.84538184932646</v>
+        <v>41.6401109568759</v>
       </c>
       <c r="D6" t="n">
-        <v>2.068154080842484</v>
+        <v>2.059013188299599</v>
       </c>
       <c r="E6" t="n">
-        <v>7.561428780329844</v>
+        <v>7.506525872319248</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469661113438413</v>
+        <v>0.7468900990516563</v>
       </c>
       <c r="G6" t="n">
-        <v>31.53191437070891</v>
+        <v>31.3901713348419</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3604411218167</v>
+        <v>34.35694455637619</v>
       </c>
       <c r="I6" t="n">
-        <v>3.833751789949589</v>
+        <v>3.805791788385562</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668538195899007</v>
+        <v>4.668063119072852</v>
       </c>
       <c r="K6" t="n">
-        <v>15.22880554910963</v>
+        <v>15.466600041653</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7982132300065</v>
+        <v>42.76661936898779</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87240062844259</v>
+        <v>99.87333036751669</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.31655723200112</v>
+        <v>82.9737881029217</v>
       </c>
       <c r="C7" t="n">
-        <v>40.98629165071772</v>
+        <v>40.67157083191844</v>
       </c>
       <c r="D7" t="n">
-        <v>1.997619329001682</v>
+        <v>1.983131737902543</v>
       </c>
       <c r="E7" t="n">
-        <v>7.836691928154946</v>
+        <v>7.759142066290222</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479220863399916</v>
+        <v>0.7478429215282303</v>
       </c>
       <c r="G7" t="n">
-        <v>30.4565129894456</v>
+        <v>30.23333963379438</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40441597163962</v>
+        <v>34.40077439029859</v>
       </c>
       <c r="I7" t="n">
-        <v>3.198881887794332</v>
+        <v>3.175539093556301</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674513039624947</v>
+        <v>4.674018259551439</v>
       </c>
       <c r="K7" t="n">
-        <v>16.68344276799888</v>
+        <v>17.02621189707829</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22377247600703</v>
+        <v>42.19650083243702</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89350689472363</v>
+        <v>99.89428356143374</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.25776564386345</v>
+        <v>88.01579028529339</v>
       </c>
       <c r="C8" t="n">
-        <v>43.33535804098514</v>
+        <v>42.97129625738423</v>
       </c>
       <c r="D8" t="n">
-        <v>2.001894939321231</v>
+        <v>1.987480174332518</v>
       </c>
       <c r="E8" t="n">
-        <v>9.702654666894222</v>
+        <v>9.599656912484029</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495229035448249</v>
+        <v>0.7494827255521989</v>
       </c>
       <c r="G8" t="n">
-        <v>30.97403849038549</v>
+        <v>30.7289001148391</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47805356306195</v>
+        <v>34.47620537540114</v>
       </c>
       <c r="I8" t="n">
-        <v>5.667082933500575</v>
+        <v>5.789797947983163</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684518147155155</v>
+        <v>4.684267034701242</v>
       </c>
       <c r="K8" t="n">
-        <v>11.74223435613655</v>
+        <v>11.9842097147066</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73390829347142</v>
+        <v>44.85192301571371</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81150069059311</v>
+        <v>99.80742898780454</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.33183252573583</v>
+        <v>86.07872818809585</v>
       </c>
       <c r="C9" t="n">
-        <v>42.28927273389321</v>
+        <v>41.93259643389683</v>
       </c>
       <c r="D9" t="n">
-        <v>1.91504846274954</v>
+        <v>1.900051148984609</v>
       </c>
       <c r="E9" t="n">
-        <v>10.07026546811515</v>
+        <v>9.983012956092269</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508920932947817</v>
+        <v>0.7508856648449065</v>
       </c>
       <c r="G9" t="n">
-        <v>29.63031857019928</v>
+        <v>29.37713931654288</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54103629155996</v>
+        <v>34.54074058286569</v>
       </c>
       <c r="I9" t="n">
-        <v>4.731196056724734</v>
+        <v>4.833863113484823</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693075583092385</v>
+        <v>4.693035405280664</v>
       </c>
       <c r="K9" t="n">
-        <v>13.66816747426418</v>
+        <v>13.92127181190416</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88514082146758</v>
+        <v>43.98530403342169</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84258102962497</v>
+        <v>99.83917227922268</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.21207957986147</v>
+        <v>84.05855196590934</v>
       </c>
       <c r="C10" t="n">
-        <v>40.90388221191841</v>
+        <v>40.66228274115106</v>
       </c>
       <c r="D10" t="n">
-        <v>1.82034351995276</v>
+        <v>1.809912243316729</v>
       </c>
       <c r="E10" t="n">
-        <v>10.23039801970953</v>
+        <v>10.181860333634</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520657737615302</v>
+        <v>0.7520870383411655</v>
       </c>
       <c r="G10" t="n">
-        <v>28.1650096342509</v>
+        <v>27.98348041895945</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59502559303039</v>
+        <v>34.59600376369361</v>
       </c>
       <c r="I10" t="n">
-        <v>3.948825953146792</v>
+        <v>4.034664178332115</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700411086009563</v>
+        <v>4.700543989632283</v>
       </c>
       <c r="K10" t="n">
-        <v>15.78792042013852</v>
+        <v>15.94144803409066</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1767752552563</v>
+        <v>43.26199524938372</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86857788731322</v>
+        <v>99.86572602462543</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.95253367089836</v>
+        <v>81.86472647232591</v>
       </c>
       <c r="C11" t="n">
-        <v>39.25671908775978</v>
+        <v>39.09388456543626</v>
       </c>
       <c r="D11" t="n">
-        <v>1.720369069182023</v>
+        <v>1.71293002771155</v>
       </c>
       <c r="E11" t="n">
-        <v>10.21772100745304</v>
+        <v>10.19741444726387</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530737275077797</v>
+        <v>0.7531180679642628</v>
       </c>
       <c r="G11" t="n">
-        <v>26.61816897573068</v>
+        <v>26.48401549109007</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64139146535787</v>
+        <v>34.64343112635608</v>
       </c>
       <c r="I11" t="n">
-        <v>3.295098628743357</v>
+        <v>3.366829387163439</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706710796923622</v>
+        <v>4.706987924776642</v>
       </c>
       <c r="K11" t="n">
-        <v>18.04746632910162</v>
+        <v>18.13527352767409</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58612497332895</v>
+        <v>42.65876790193599</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89031039019035</v>
+        <v>99.88792599504633</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.55951314010073</v>
+        <v>79.57541861107573</v>
       </c>
       <c r="C12" t="n">
-        <v>37.37396483640133</v>
+        <v>37.32578536544116</v>
       </c>
       <c r="D12" t="n">
-        <v>1.615451711159203</v>
+        <v>1.612689960145135</v>
       </c>
       <c r="E12" t="n">
-        <v>10.05276913679783</v>
+        <v>10.06883072776804</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753941111146993</v>
+        <v>0.7540042306505229</v>
       </c>
       <c r="G12" t="n">
-        <v>24.99484987847064</v>
+        <v>24.93418014504061</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68129111276168</v>
+        <v>34.68419460992405</v>
       </c>
       <c r="I12" t="n">
-        <v>2.749078245095681</v>
+        <v>2.808992495981611</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712131944668706</v>
+        <v>4.712526441565767</v>
       </c>
       <c r="K12" t="n">
-        <v>20.44048685989928</v>
+        <v>20.42458138892427</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09401778623429</v>
+        <v>42.15611020710226</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9084694825349</v>
+        <v>99.90647696146769</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.20188800789525</v>
+        <v>77.30506171124867</v>
       </c>
       <c r="C13" t="n">
-        <v>35.44120312829916</v>
+        <v>35.48948601044137</v>
       </c>
       <c r="D13" t="n">
-        <v>1.513066439031077</v>
+        <v>1.514223478579804</v>
       </c>
       <c r="E13" t="n">
-        <v>9.797831897222705</v>
+        <v>9.844587220080539</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754687600974299</v>
+        <v>0.7547660508866363</v>
       </c>
       <c r="G13" t="n">
-        <v>23.41070812484773</v>
+        <v>23.41176663080422</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71562964481776</v>
+        <v>34.71923834078526</v>
       </c>
       <c r="I13" t="n">
-        <v>2.293166794912315</v>
+        <v>2.343192172070746</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716797506089368</v>
+        <v>4.717287818041475</v>
       </c>
       <c r="K13" t="n">
-        <v>22.79811199210474</v>
+        <v>22.69493828875132</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68432159501013</v>
+        <v>41.73754813147449</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92363671541402</v>
+        <v>99.92197243066717</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.87728759691493</v>
+        <v>83.78696680812422</v>
       </c>
       <c r="C14" t="n">
-        <v>39.58032264934135</v>
+        <v>39.40709646020496</v>
       </c>
       <c r="D14" t="n">
-        <v>1.514848720069686</v>
+        <v>1.516129787976142</v>
       </c>
       <c r="E14" t="n">
-        <v>12.11080763585588</v>
+        <v>12.06400682288082</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555765674906345</v>
+        <v>0.7557162525148607</v>
       </c>
       <c r="G14" t="n">
-        <v>25.24571243642893</v>
+        <v>25.12085458182127</v>
       </c>
       <c r="H14" t="n">
-        <v>36.56395032291682</v>
+        <v>36.44256166714452</v>
       </c>
       <c r="I14" t="n">
-        <v>2.964038367336515</v>
+        <v>3.164471117568738</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722353546816465</v>
+        <v>4.723226578217878</v>
       </c>
       <c r="K14" t="n">
-        <v>16.12271240308507</v>
+        <v>16.21303319187578</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19827991237942</v>
+        <v>44.27452060584328</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90131496480583</v>
+        <v>99.89465025792401</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.13620552488716</v>
+        <v>83.14511979404173</v>
       </c>
       <c r="C15" t="n">
-        <v>39.29740111109454</v>
+        <v>39.2543703085507</v>
       </c>
       <c r="D15" t="n">
-        <v>1.487425545276654</v>
+        <v>1.492563079906468</v>
       </c>
       <c r="E15" t="n">
-        <v>12.30378114367948</v>
+        <v>12.3164590311784</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563255987134974</v>
+        <v>0.7565160499707493</v>
       </c>
       <c r="G15" t="n">
-        <v>24.78882580234146</v>
+        <v>24.73037623947513</v>
       </c>
       <c r="H15" t="n">
-        <v>36.60033183534706</v>
+        <v>36.48112993666426</v>
       </c>
       <c r="I15" t="n">
-        <v>2.472480607569656</v>
+        <v>2.639850144529552</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727034991959358</v>
+        <v>4.728225312317182</v>
       </c>
       <c r="K15" t="n">
-        <v>16.86379447511282</v>
+        <v>16.85488020595826</v>
       </c>
       <c r="L15" t="n">
-        <v>43.75647001469996</v>
+        <v>43.80284751000301</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91766560090733</v>
+        <v>99.91209802451198</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.65258018268358</v>
+        <v>80.79813409731523</v>
       </c>
       <c r="C16" t="n">
-        <v>37.19613283219218</v>
+        <v>37.31557455721112</v>
       </c>
       <c r="D16" t="n">
-        <v>1.392857240436708</v>
+        <v>1.402941707945271</v>
       </c>
       <c r="E16" t="n">
-        <v>11.8652177876566</v>
+        <v>11.94389267663188</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569701996173657</v>
+        <v>0.7572032575100172</v>
       </c>
       <c r="G16" t="n">
-        <v>23.21278911092902</v>
+        <v>23.24543380887633</v>
       </c>
       <c r="H16" t="n">
-        <v>36.63152555273951</v>
+        <v>36.51426883376295</v>
       </c>
       <c r="I16" t="n">
-        <v>2.062156543695854</v>
+        <v>2.201873453151186</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731063747608535</v>
+        <v>4.732520359437606</v>
       </c>
       <c r="K16" t="n">
-        <v>19.3474198173164</v>
+        <v>19.20186590268477</v>
       </c>
       <c r="L16" t="n">
-        <v>43.38776733361447</v>
+        <v>43.40923036942273</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93131998312306</v>
+        <v>99.92667082931862</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.29257008767381</v>
+        <v>82.44137358720651</v>
       </c>
       <c r="C17" t="n">
-        <v>38.38842748673957</v>
+        <v>38.50670299611513</v>
       </c>
       <c r="D17" t="n">
-        <v>1.394022972900016</v>
+        <v>1.404202289280977</v>
       </c>
       <c r="E17" t="n">
-        <v>12.62811451183736</v>
+        <v>12.71894981305875</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576037352804849</v>
+        <v>0.7578836252604</v>
       </c>
       <c r="G17" t="n">
-        <v>23.64081492631255</v>
+        <v>23.66026658994196</v>
       </c>
       <c r="H17" t="n">
-        <v>37.07078199264984</v>
+        <v>36.94102402449408</v>
       </c>
       <c r="I17" t="n">
-        <v>2.066208603190528</v>
+        <v>2.222274587292848</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73502334550303</v>
+        <v>4.736772657877498</v>
       </c>
       <c r="K17" t="n">
-        <v>17.70742991232619</v>
+        <v>17.5586264127935</v>
       </c>
       <c r="L17" t="n">
-        <v>43.83532657544173</v>
+        <v>43.86066127090488</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9311839745075</v>
+        <v>99.92599067981351</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.86626899392121</v>
+        <v>80.12236770005103</v>
       </c>
       <c r="C18" t="n">
-        <v>36.2812284696876</v>
+        <v>36.53094567862173</v>
       </c>
       <c r="D18" t="n">
-        <v>1.305155955944106</v>
+        <v>1.319033811429914</v>
       </c>
       <c r="E18" t="n">
-        <v>12.11026964875332</v>
+        <v>12.25640004607558</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581485672546403</v>
+        <v>0.7584679828610061</v>
       </c>
       <c r="G18" t="n">
-        <v>22.13374600295212</v>
+        <v>22.22521061090096</v>
       </c>
       <c r="H18" t="n">
-        <v>37.09744150658302</v>
+        <v>36.96950698341204</v>
       </c>
       <c r="I18" t="n">
-        <v>1.723078767092484</v>
+        <v>1.853323372490241</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738428545341501</v>
+        <v>4.740424892881287</v>
       </c>
       <c r="K18" t="n">
-        <v>20.1337310060788</v>
+        <v>19.87763229994898</v>
       </c>
       <c r="L18" t="n">
-        <v>43.52764584081164</v>
+        <v>43.52969217178229</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94260531657805</v>
+        <v>99.93827015035299</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.85265375919454</v>
+        <v>79.17165304073548</v>
       </c>
       <c r="C19" t="n">
-        <v>35.53302143560704</v>
+        <v>35.86580381590888</v>
       </c>
       <c r="D19" t="n">
-        <v>1.268712085611121</v>
+        <v>1.284841282247713</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01157643199076</v>
+        <v>12.1962581860699</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586090404240275</v>
+        <v>0.758961496015077</v>
       </c>
       <c r="G19" t="n">
-        <v>21.51570540355776</v>
+        <v>21.64907969158057</v>
       </c>
       <c r="H19" t="n">
-        <v>37.11997320710255</v>
+        <v>36.99356197110843</v>
       </c>
       <c r="I19" t="n">
-        <v>1.436771087858138</v>
+        <v>1.545441063619545</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741306502650171</v>
+        <v>4.74350935009423</v>
       </c>
       <c r="K19" t="n">
-        <v>21.14734624080546</v>
+        <v>20.82834695926454</v>
       </c>
       <c r="L19" t="n">
-        <v>43.27176902450159</v>
+        <v>43.25436802003519</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9521367009141</v>
+        <v>99.9485187952086</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.32255248067192</v>
+        <v>76.58596520719837</v>
       </c>
       <c r="C20" t="n">
-        <v>33.22405322304135</v>
+        <v>33.51809741454556</v>
       </c>
       <c r="D20" t="n">
-        <v>1.177076459154148</v>
+        <v>1.190940624245016</v>
       </c>
       <c r="E20" t="n">
-        <v>11.34366884884092</v>
+        <v>11.51967830409284</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590059370126825</v>
+        <v>0.7593871571560062</v>
       </c>
       <c r="G20" t="n">
-        <v>19.9616844671457</v>
+        <v>20.06688984737201</v>
       </c>
       <c r="H20" t="n">
-        <v>37.1393940022049</v>
+        <v>37.01430969267052</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1979356599843</v>
+        <v>1.288589849436937</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743787106329265</v>
+        <v>4.746169732225038</v>
       </c>
       <c r="K20" t="n">
-        <v>23.67744751932809</v>
+        <v>23.41403479280163</v>
       </c>
       <c r="L20" t="n">
-        <v>43.0585889496345</v>
+        <v>43.02493887421895</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96008969200393</v>
+        <v>99.95707108156614</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.17022468877059</v>
+        <v>82.17037195092621</v>
       </c>
       <c r="C21" t="n">
-        <v>36.84422906305803</v>
+        <v>36.89722945296111</v>
       </c>
       <c r="D21" t="n">
-        <v>1.177902057845233</v>
+        <v>1.191873262174513</v>
       </c>
       <c r="E21" t="n">
-        <v>13.29837045394394</v>
+        <v>13.37105317134999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595383020117871</v>
+        <v>0.7599818410986966</v>
       </c>
       <c r="G21" t="n">
-        <v>21.63426070583832</v>
+        <v>21.6032157806217</v>
       </c>
       <c r="H21" t="n">
-        <v>38.82401864641757</v>
+        <v>38.56390732581275</v>
       </c>
       <c r="I21" t="n">
-        <v>1.729020135140063</v>
+        <v>1.930454063001703</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747114387573668</v>
+        <v>4.749886506866853</v>
       </c>
       <c r="K21" t="n">
-        <v>17.82977531122943</v>
+        <v>17.82962804907379</v>
       </c>
       <c r="L21" t="n">
-        <v>45.26840201723093</v>
+        <v>45.20884438171871</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94240639151839</v>
+        <v>99.93570188375361</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_99_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_99_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.37568888395052</v>
+        <v>45.55754209200187</v>
       </c>
       <c r="M2" t="n">
-        <v>99.6434918508721</v>
+        <v>99.59890649113149</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01865439383022</v>
+        <v>88.03136802660019</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93980913831557</v>
+        <v>45.94255769100285</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228699973742813</v>
+        <v>2.228730505232563</v>
       </c>
       <c r="E3" t="n">
-        <v>5.712165949511832</v>
+        <v>5.714443332426353</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428999912476044</v>
+        <v>0.7429101684108543</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97708884396182</v>
+        <v>33.97790758324062</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1733995973898</v>
+        <v>34.17386774689929</v>
       </c>
       <c r="I3" t="n">
-        <v>6.541275092678821</v>
+        <v>6.550320137822676</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643124945297528</v>
+        <v>4.643188552567839</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98134560616979</v>
+        <v>11.96863197339979</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84404379565932</v>
+        <v>48.85368742154584</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7651985401447</v>
+        <v>106.7648770859485</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.06821152440783</v>
+        <v>87.12259629635463</v>
       </c>
       <c r="C4" t="n">
-        <v>42.61892231858042</v>
+        <v>42.66498654487354</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182721795669168</v>
+        <v>2.184979011682771</v>
       </c>
       <c r="E4" t="n">
-        <v>6.504734074797008</v>
+        <v>6.513935615579185</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444535866089886</v>
+        <v>0.744464964645996</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27614001294073</v>
+        <v>33.31089817991734</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24486498401348</v>
+        <v>34.24538837371581</v>
       </c>
       <c r="I4" t="n">
-        <v>5.462462154072272</v>
+        <v>5.470024121776069</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652834916306179</v>
+        <v>4.652906029037474</v>
       </c>
       <c r="K4" t="n">
-        <v>12.93178847559217</v>
+        <v>12.87740370364535</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26758711991968</v>
+        <v>44.27565641431936</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81829791409227</v>
+        <v>99.81804666283826</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.90071729651065</v>
+        <v>85.95456736810377</v>
       </c>
       <c r="C5" t="n">
-        <v>42.29923054129543</v>
+        <v>42.3459744160433</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125749916294192</v>
+        <v>2.127990202682718</v>
       </c>
       <c r="E5" t="n">
-        <v>7.09496984534041</v>
+        <v>7.105109537242112</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457709166409296</v>
+        <v>0.7457833137980232</v>
       </c>
       <c r="G5" t="n">
-        <v>32.40758945434749</v>
+        <v>32.44208049158014</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30546216548277</v>
+        <v>34.30603243470905</v>
       </c>
       <c r="I5" t="n">
-        <v>4.560106769399054</v>
+        <v>4.566425676854068</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66106822900581</v>
+        <v>4.661145711237644</v>
       </c>
       <c r="K5" t="n">
-        <v>14.09928270348933</v>
+        <v>14.04543263189624</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44975169537989</v>
+        <v>43.45664783756667</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84826494016465</v>
+        <v>99.8480548855062</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.533399958347</v>
+        <v>84.53801910182358</v>
       </c>
       <c r="C6" t="n">
-        <v>41.6401109568759</v>
+        <v>41.63864106747477</v>
       </c>
       <c r="D6" t="n">
-        <v>2.059013188299599</v>
+        <v>2.058748412920647</v>
       </c>
       <c r="E6" t="n">
-        <v>7.506525872319248</v>
+        <v>7.509098170922734</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468900990516563</v>
+        <v>0.7469040066828797</v>
       </c>
       <c r="G6" t="n">
-        <v>31.3901713348419</v>
+        <v>31.3864611029146</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35694455637619</v>
+        <v>34.35758430741245</v>
       </c>
       <c r="I6" t="n">
-        <v>3.805791788385562</v>
+        <v>3.811073059202267</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668063119072852</v>
+        <v>4.668150041767997</v>
       </c>
       <c r="K6" t="n">
-        <v>15.466600041653</v>
+        <v>15.46198089817643</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76661936898779</v>
+        <v>42.77253287665842</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87333036751669</v>
+        <v>99.87315484230962</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.9737881029217</v>
+        <v>82.90641576008393</v>
       </c>
       <c r="C7" t="n">
-        <v>40.67157083191844</v>
+        <v>40.59892405436818</v>
       </c>
       <c r="D7" t="n">
-        <v>1.983131737902543</v>
+        <v>1.979256004878225</v>
       </c>
       <c r="E7" t="n">
-        <v>7.759142066290222</v>
+        <v>7.74914926973737</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478429215282303</v>
+        <v>0.7478589472155563</v>
       </c>
       <c r="G7" t="n">
-        <v>30.23333963379438</v>
+        <v>30.17456684845299</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40077439029859</v>
+        <v>34.40151157191558</v>
       </c>
       <c r="I7" t="n">
-        <v>3.175539093556301</v>
+        <v>3.179954697786989</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674018259551439</v>
+        <v>4.674118420097225</v>
       </c>
       <c r="K7" t="n">
-        <v>17.02621189707829</v>
+        <v>17.09358423991609</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19650083243702</v>
+        <v>42.20162856518233</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89428356143374</v>
+        <v>99.89413685946661</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.01579028529339</v>
+        <v>87.81654033525911</v>
       </c>
       <c r="C8" t="n">
-        <v>42.97129625738423</v>
+        <v>42.9263281021802</v>
       </c>
       <c r="D8" t="n">
-        <v>1.987480174332518</v>
+        <v>1.983492542546982</v>
       </c>
       <c r="E8" t="n">
-        <v>9.599656912484029</v>
+        <v>9.599262284144366</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494827255521989</v>
+        <v>0.7494597166930708</v>
       </c>
       <c r="G8" t="n">
-        <v>30.7289001148391</v>
+        <v>30.6859960669393</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47620537540114</v>
+        <v>34.47514696788124</v>
       </c>
       <c r="I8" t="n">
-        <v>5.789797947983163</v>
+        <v>5.639059527722448</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684267034701242</v>
+        <v>4.684123229331691</v>
       </c>
       <c r="K8" t="n">
-        <v>11.9842097147066</v>
+        <v>12.1834596647409</v>
       </c>
       <c r="L8" t="n">
-        <v>44.85192301571371</v>
+        <v>44.70264506401227</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80742898780454</v>
+        <v>99.81243283093336</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.07872818809585</v>
+        <v>85.71784850219366</v>
       </c>
       <c r="C9" t="n">
-        <v>41.93259643389683</v>
+        <v>41.70272148944194</v>
       </c>
       <c r="D9" t="n">
-        <v>1.900051148984609</v>
+        <v>1.888460836632497</v>
       </c>
       <c r="E9" t="n">
-        <v>9.983012956092269</v>
+        <v>9.923985705411297</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508856648449065</v>
+        <v>0.7508317844718766</v>
       </c>
       <c r="G9" t="n">
-        <v>29.37713931654288</v>
+        <v>29.21579010882571</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54074058286569</v>
+        <v>34.53826208570631</v>
       </c>
       <c r="I9" t="n">
-        <v>4.833863113484823</v>
+        <v>4.707819328196732</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693035405280664</v>
+        <v>4.692698652949227</v>
       </c>
       <c r="K9" t="n">
-        <v>13.92127181190416</v>
+        <v>14.28215149780635</v>
       </c>
       <c r="L9" t="n">
-        <v>43.98530403342169</v>
+        <v>43.85848647031497</v>
       </c>
       <c r="M9" t="n">
-        <v>99.83917227922268</v>
+        <v>99.84335945756327</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.05855196590934</v>
+        <v>83.50398198378943</v>
       </c>
       <c r="C10" t="n">
-        <v>40.66228274115106</v>
+        <v>40.21906571252002</v>
       </c>
       <c r="D10" t="n">
-        <v>1.809912243316729</v>
+        <v>1.78936253850351</v>
       </c>
       <c r="E10" t="n">
-        <v>10.181860333634</v>
+        <v>10.05810703698353</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520870383411655</v>
+        <v>0.7520094810605161</v>
       </c>
       <c r="G10" t="n">
-        <v>27.98348041895945</v>
+        <v>27.68267116766669</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59600376369361</v>
+        <v>34.59243612878372</v>
       </c>
       <c r="I10" t="n">
-        <v>4.034664178332115</v>
+        <v>3.929336374163246</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700543989632283</v>
+        <v>4.700059256628225</v>
       </c>
       <c r="K10" t="n">
-        <v>15.94144803409066</v>
+        <v>16.49601801621058</v>
       </c>
       <c r="L10" t="n">
-        <v>43.26199524938372</v>
+        <v>43.15414351215281</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86572602462543</v>
+        <v>99.8692272408834</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.86472647232591</v>
+        <v>81.04114371103145</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09388456543626</v>
+        <v>38.36505311453451</v>
       </c>
       <c r="D11" t="n">
-        <v>1.71293002771155</v>
+        <v>1.680143108907689</v>
       </c>
       <c r="E11" t="n">
-        <v>10.19741444726387</v>
+        <v>9.990655678865034</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7531180679642628</v>
+        <v>0.7530236721141623</v>
       </c>
       <c r="G11" t="n">
-        <v>26.48401549109007</v>
+        <v>25.99297135023905</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64343112635608</v>
+        <v>34.63908891725145</v>
       </c>
       <c r="I11" t="n">
-        <v>3.366829387163439</v>
+        <v>3.278863032940546</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706987924776642</v>
+        <v>4.706397950713513</v>
       </c>
       <c r="K11" t="n">
-        <v>18.13527352767409</v>
+        <v>18.95885628896854</v>
       </c>
       <c r="L11" t="n">
-        <v>42.65876790193599</v>
+        <v>42.56694236388132</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88792599504633</v>
+        <v>99.89085176738438</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.57541861107573</v>
+        <v>78.53999537158968</v>
       </c>
       <c r="C12" t="n">
-        <v>37.32578536544116</v>
+        <v>36.37104311414814</v>
       </c>
       <c r="D12" t="n">
-        <v>1.612689960145135</v>
+        <v>1.570390499309184</v>
       </c>
       <c r="E12" t="n">
-        <v>10.06883072776804</v>
+        <v>9.793958745625099</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7540042306505229</v>
+        <v>0.7538979358361497</v>
       </c>
       <c r="G12" t="n">
-        <v>24.93418014504061</v>
+        <v>24.29502287086065</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68419460992405</v>
+        <v>34.67930504846287</v>
       </c>
       <c r="I12" t="n">
-        <v>2.808992495981611</v>
+        <v>2.735558172519816</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712526441565767</v>
+        <v>4.711862098975934</v>
       </c>
       <c r="K12" t="n">
-        <v>20.42458138892427</v>
+        <v>21.46000462841031</v>
       </c>
       <c r="L12" t="n">
-        <v>42.15611020710226</v>
+        <v>42.07787272874875</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90647696146769</v>
+        <v>99.9089204713072</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.30506171124867</v>
+        <v>76.0220621948952</v>
       </c>
       <c r="C13" t="n">
-        <v>35.48948601044137</v>
+        <v>34.27527551000877</v>
       </c>
       <c r="D13" t="n">
-        <v>1.514223478579804</v>
+        <v>1.460964433672504</v>
       </c>
       <c r="E13" t="n">
-        <v>9.844587220080539</v>
+        <v>9.491826651310646</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547660508866363</v>
+        <v>0.7546522472465347</v>
       </c>
       <c r="G13" t="n">
-        <v>23.41176663080422</v>
+        <v>22.60212625152876</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71923834078526</v>
+        <v>34.71400337334057</v>
       </c>
       <c r="I13" t="n">
-        <v>2.343192172070746</v>
+        <v>2.281912692505339</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717287818041475</v>
+        <v>4.71657654529084</v>
       </c>
       <c r="K13" t="n">
-        <v>22.69493828875132</v>
+        <v>23.97793780510482</v>
       </c>
       <c r="L13" t="n">
-        <v>41.73754813147449</v>
+        <v>41.67079895787198</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92197243066717</v>
+        <v>99.92401227298556</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.78696680812422</v>
+        <v>83.09963542290399</v>
       </c>
       <c r="C14" t="n">
-        <v>39.40709646020496</v>
+        <v>38.64060870757494</v>
       </c>
       <c r="D14" t="n">
-        <v>1.516129787976142</v>
+        <v>1.462732633248296</v>
       </c>
       <c r="E14" t="n">
-        <v>12.06400682288082</v>
+        <v>11.92289296846187</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7557162525148607</v>
+        <v>0.7555655999282951</v>
       </c>
       <c r="G14" t="n">
-        <v>25.12085458182127</v>
+        <v>24.54618408447208</v>
       </c>
       <c r="H14" t="n">
-        <v>36.44256166714452</v>
+        <v>36.6727201640896</v>
       </c>
       <c r="I14" t="n">
-        <v>3.164471117568738</v>
+        <v>3.017254973152006</v>
       </c>
       <c r="J14" t="n">
-        <v>4.723226578217878</v>
+        <v>4.722284999551842</v>
       </c>
       <c r="K14" t="n">
-        <v>16.21303319187578</v>
+        <v>16.90036457709601</v>
       </c>
       <c r="L14" t="n">
-        <v>44.27452060584328</v>
+        <v>44.35857312814346</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89465025792401</v>
+        <v>99.89954641281442</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.14511979404173</v>
+        <v>82.33419619033387</v>
       </c>
       <c r="C15" t="n">
-        <v>39.2543703085507</v>
+        <v>38.34099924425598</v>
       </c>
       <c r="D15" t="n">
-        <v>1.492563079906468</v>
+        <v>1.434676078667855</v>
       </c>
       <c r="E15" t="n">
-        <v>12.3164590311784</v>
+        <v>12.11369115058444</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7565160499707493</v>
+        <v>0.7563355166567683</v>
       </c>
       <c r="G15" t="n">
-        <v>24.73037623947513</v>
+        <v>24.07536574224491</v>
       </c>
       <c r="H15" t="n">
-        <v>36.48112993666426</v>
+        <v>36.71008944180107</v>
       </c>
       <c r="I15" t="n">
-        <v>2.639850144529552</v>
+        <v>2.516941281274031</v>
       </c>
       <c r="J15" t="n">
-        <v>4.728225312317182</v>
+        <v>4.7270969791048</v>
       </c>
       <c r="K15" t="n">
-        <v>16.85488020595826</v>
+        <v>17.66580380966613</v>
       </c>
       <c r="L15" t="n">
-        <v>43.80284751000301</v>
+        <v>43.90938430793477</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91209802451198</v>
+        <v>99.91618736185688</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.79813409731523</v>
+        <v>79.89737076119172</v>
       </c>
       <c r="C16" t="n">
-        <v>37.31557455721112</v>
+        <v>36.29281823696657</v>
       </c>
       <c r="D16" t="n">
-        <v>1.402941707945271</v>
+        <v>1.342929684949301</v>
       </c>
       <c r="E16" t="n">
-        <v>11.94389267663188</v>
+        <v>11.68891158517636</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7572032575100172</v>
+        <v>0.7569979356714431</v>
       </c>
       <c r="G16" t="n">
-        <v>23.24543380887633</v>
+        <v>22.5357652587984</v>
       </c>
       <c r="H16" t="n">
-        <v>36.51426883376295</v>
+        <v>36.7422411267889</v>
       </c>
       <c r="I16" t="n">
-        <v>2.201873453151186</v>
+        <v>2.099288071860804</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732520359437606</v>
+        <v>4.731237097946518</v>
       </c>
       <c r="K16" t="n">
-        <v>19.20186590268477</v>
+        <v>20.10262923880826</v>
       </c>
       <c r="L16" t="n">
-        <v>43.40923036942273</v>
+        <v>43.53463748863422</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92667082931862</v>
+        <v>99.93008496440906</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.44137358720651</v>
+        <v>81.76328044788323</v>
       </c>
       <c r="C17" t="n">
-        <v>38.50670299611513</v>
+        <v>37.63407663371738</v>
       </c>
       <c r="D17" t="n">
-        <v>1.404202289280977</v>
+        <v>1.344083850230601</v>
       </c>
       <c r="E17" t="n">
-        <v>12.71894981305875</v>
+        <v>12.52993252242467</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578836252604</v>
+        <v>0.7576485287331346</v>
       </c>
       <c r="G17" t="n">
-        <v>23.66026658994196</v>
+        <v>23.03475590129867</v>
       </c>
       <c r="H17" t="n">
-        <v>36.94102402449408</v>
+        <v>37.25344135956053</v>
       </c>
       <c r="I17" t="n">
-        <v>2.222274587292848</v>
+        <v>2.108114981053541</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736772657877498</v>
+        <v>4.735303304582089</v>
       </c>
       <c r="K17" t="n">
-        <v>17.5586264127935</v>
+        <v>18.23671955211677</v>
       </c>
       <c r="L17" t="n">
-        <v>43.86066127090488</v>
+        <v>44.05899365610024</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92599067981351</v>
+        <v>99.92978984193439</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.12236770005103</v>
+        <v>79.46414513426171</v>
       </c>
       <c r="C18" t="n">
-        <v>36.53094567862173</v>
+        <v>35.6600792364341</v>
       </c>
       <c r="D18" t="n">
-        <v>1.319033811429914</v>
+        <v>1.261287134829966</v>
       </c>
       <c r="E18" t="n">
-        <v>12.25640004607558</v>
+        <v>12.05108762847772</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584679828610061</v>
+        <v>0.7582072671343375</v>
       </c>
       <c r="G18" t="n">
-        <v>22.22521061090096</v>
+        <v>21.61579522532916</v>
       </c>
       <c r="H18" t="n">
-        <v>36.96950698341204</v>
+        <v>37.28091442586391</v>
       </c>
       <c r="I18" t="n">
-        <v>1.853323372490241</v>
+        <v>1.758058033037021</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740424892881287</v>
+        <v>4.738795419589607</v>
       </c>
       <c r="K18" t="n">
-        <v>19.87763229994898</v>
+        <v>20.53585486573829</v>
       </c>
       <c r="L18" t="n">
-        <v>43.52969217178229</v>
+        <v>43.7455071483539</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93827015035299</v>
+        <v>99.94144125052628</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.17165304073548</v>
+        <v>78.59690848223825</v>
       </c>
       <c r="C19" t="n">
-        <v>35.86580381590888</v>
+        <v>35.06331533055841</v>
       </c>
       <c r="D19" t="n">
-        <v>1.284841282247713</v>
+        <v>1.230735149503989</v>
       </c>
       <c r="E19" t="n">
-        <v>12.1962581860699</v>
+        <v>12.00350232047151</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758961496015077</v>
+        <v>0.7586786601144122</v>
       </c>
       <c r="G19" t="n">
-        <v>21.64907969158057</v>
+        <v>21.09219878142932</v>
       </c>
       <c r="H19" t="n">
-        <v>36.99356197110843</v>
+        <v>37.30409273358119</v>
       </c>
       <c r="I19" t="n">
-        <v>1.545441063619545</v>
+        <v>1.465959211422755</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74350935009423</v>
+        <v>4.741741625715075</v>
       </c>
       <c r="K19" t="n">
-        <v>20.82834695926454</v>
+        <v>21.40309151776176</v>
       </c>
       <c r="L19" t="n">
-        <v>43.25436802003519</v>
+        <v>43.48475820631771</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9485187952086</v>
+        <v>99.95116505463787</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.58596520719837</v>
+        <v>76.1058218574824</v>
       </c>
       <c r="C20" t="n">
-        <v>33.51809741454556</v>
+        <v>32.79763373279431</v>
       </c>
       <c r="D20" t="n">
-        <v>1.190940624245016</v>
+        <v>1.142031138757569</v>
       </c>
       <c r="E20" t="n">
-        <v>11.51967830409284</v>
+        <v>11.34207628502921</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593871571560062</v>
+        <v>0.7590848151196027</v>
       </c>
       <c r="G20" t="n">
-        <v>20.06688984737201</v>
+        <v>19.57199955080885</v>
       </c>
       <c r="H20" t="n">
-        <v>37.01430969267052</v>
+        <v>37.32406330185255</v>
       </c>
       <c r="I20" t="n">
-        <v>1.288589849436937</v>
+        <v>1.222286671417104</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746169732225038</v>
+        <v>4.744280094497515</v>
       </c>
       <c r="K20" t="n">
-        <v>23.41403479280163</v>
+        <v>23.89417814251761</v>
       </c>
       <c r="L20" t="n">
-        <v>43.02493887421895</v>
+        <v>43.26746703548189</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95707108156614</v>
+        <v>99.95927891079381</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.17037195092621</v>
+        <v>82.02690915890462</v>
       </c>
       <c r="C21" t="n">
-        <v>36.89722945296111</v>
+        <v>36.46802560330845</v>
       </c>
       <c r="D21" t="n">
-        <v>1.191873262174513</v>
+        <v>1.142844664850244</v>
       </c>
       <c r="E21" t="n">
-        <v>13.37105317134999</v>
+        <v>13.32395348011676</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599818410986966</v>
+        <v>0.7596255493278881</v>
       </c>
       <c r="G21" t="n">
-        <v>21.6032157806217</v>
+        <v>21.26757991378925</v>
       </c>
       <c r="H21" t="n">
-        <v>38.56390732581275</v>
+        <v>39.03228935072556</v>
       </c>
       <c r="I21" t="n">
-        <v>1.930454063001703</v>
+        <v>1.752956516795612</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749886506866853</v>
+        <v>4.747659683299299</v>
       </c>
       <c r="K21" t="n">
-        <v>17.82962804907379</v>
+        <v>17.97309084109538</v>
       </c>
       <c r="L21" t="n">
-        <v>45.20884438171871</v>
+        <v>45.50049326603655</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93570188375361</v>
+        <v>99.94160971044037</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_99_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_99_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.55754209200187</v>
+        <v>43.65883639099508</v>
       </c>
       <c r="M2" t="n">
-        <v>99.59890649113149</v>
+        <v>96.63833846850756</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03136802660019</v>
+        <v>81.42056764551025</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94255769100285</v>
+        <v>43.17612320106581</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228730505232563</v>
+        <v>2.177404663740556</v>
       </c>
       <c r="E3" t="n">
-        <v>5.714443332426353</v>
+        <v>4.141225268819161</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429101684108543</v>
+        <v>0.7375931941222582</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97790758324062</v>
+        <v>32.75179515043087</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17386774689929</v>
+        <v>33.92928692962388</v>
       </c>
       <c r="I3" t="n">
-        <v>6.550320137822676</v>
+        <v>3.07330497550941</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643188552567839</v>
+        <v>4.609957463264114</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96863197339979</v>
+        <v>18.57943235448975</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85368742154584</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7648770859485</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.12259629635463</v>
+        <v>88.4174930268552</v>
       </c>
       <c r="C4" t="n">
-        <v>42.66498654487354</v>
+        <v>42.79592047919809</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184979011682771</v>
+        <v>2.183045440738774</v>
       </c>
       <c r="E4" t="n">
-        <v>6.513935615579185</v>
+        <v>6.530805366700183</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744464964645996</v>
+        <v>0.7395040005023179</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31089817991734</v>
+        <v>33.45343263497588</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24538837371581</v>
+        <v>34.01718402310662</v>
       </c>
       <c r="I4" t="n">
-        <v>5.470024121776069</v>
+        <v>6.871621557691944</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652906029037474</v>
+        <v>4.621900003139487</v>
       </c>
       <c r="K4" t="n">
-        <v>12.87740370364535</v>
+        <v>11.58250697314481</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27565641431936</v>
+        <v>45.39311034911616</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81804666283826</v>
+        <v>99.77153780145905</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.95456736810377</v>
+        <v>87.07216845883994</v>
       </c>
       <c r="C5" t="n">
-        <v>42.3459744160433</v>
+        <v>42.51585475791468</v>
       </c>
       <c r="D5" t="n">
-        <v>2.127990202682718</v>
+        <v>2.118039683154002</v>
       </c>
       <c r="E5" t="n">
-        <v>7.105109537242112</v>
+        <v>7.292822628980183</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457833137980232</v>
+        <v>0.7411286923430278</v>
       </c>
       <c r="G5" t="n">
-        <v>32.44208049158014</v>
+        <v>32.45727117554617</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30603243470905</v>
+        <v>34.09191984777928</v>
       </c>
       <c r="I5" t="n">
-        <v>4.566425676854068</v>
+        <v>5.738932103893363</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661145711237644</v>
+        <v>4.632054327143924</v>
       </c>
       <c r="K5" t="n">
-        <v>14.04543263189624</v>
+        <v>12.92783154116005</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45664783756667</v>
+        <v>44.36543532432273</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8480548855062</v>
+        <v>99.80912162339746</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.53801910182358</v>
+        <v>85.39758320834083</v>
       </c>
       <c r="C6" t="n">
-        <v>41.63864106747477</v>
+        <v>41.73175083284281</v>
       </c>
       <c r="D6" t="n">
-        <v>2.058748412920647</v>
+        <v>2.037127963706839</v>
       </c>
       <c r="E6" t="n">
-        <v>7.509098170922734</v>
+        <v>7.812792453004855</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469040066828797</v>
+        <v>0.7425147717263932</v>
       </c>
       <c r="G6" t="n">
-        <v>31.3864611029146</v>
+        <v>31.2173635192998</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35758430741245</v>
+        <v>34.15567949941409</v>
       </c>
       <c r="I6" t="n">
-        <v>3.811073059202267</v>
+        <v>4.7913876778989</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668150041767997</v>
+        <v>4.640717323289957</v>
       </c>
       <c r="K6" t="n">
-        <v>15.46198089817643</v>
+        <v>14.60241679165915</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77253287665842</v>
+        <v>43.50641759483434</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87315484230962</v>
+        <v>99.8405852193363</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.90641576008393</v>
+        <v>83.45741548952437</v>
       </c>
       <c r="C7" t="n">
-        <v>40.59892405436818</v>
+        <v>40.53510149974069</v>
       </c>
       <c r="D7" t="n">
-        <v>1.979256004878225</v>
+        <v>1.943986818450143</v>
       </c>
       <c r="E7" t="n">
-        <v>7.74914926973737</v>
+        <v>8.122111033507379</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478589472155563</v>
+        <v>0.74370079202924</v>
       </c>
       <c r="G7" t="n">
-        <v>30.17456684845299</v>
+        <v>29.79004965297234</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40151157191558</v>
+        <v>34.21023643334505</v>
       </c>
       <c r="I7" t="n">
-        <v>3.179954697786989</v>
+        <v>3.999200809037466</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674118420097225</v>
+        <v>4.648129950182749</v>
       </c>
       <c r="K7" t="n">
-        <v>17.09358423991609</v>
+        <v>16.54258451047564</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20162856518233</v>
+        <v>42.78921988761979</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89413685946661</v>
+        <v>99.86690589783612</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.81654033525911</v>
+        <v>81.28884566067276</v>
       </c>
       <c r="C8" t="n">
-        <v>42.9263281021802</v>
+        <v>38.98672302491828</v>
       </c>
       <c r="D8" t="n">
-        <v>1.983492542546982</v>
+        <v>1.840730181875968</v>
       </c>
       <c r="E8" t="n">
-        <v>9.599262284144366</v>
+        <v>8.246902345931204</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494597166930708</v>
+        <v>0.7447185204646392</v>
       </c>
       <c r="G8" t="n">
-        <v>30.6859960669393</v>
+        <v>28.20772393895543</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47514696788124</v>
+        <v>34.2570519413734</v>
       </c>
       <c r="I8" t="n">
-        <v>5.639059527722448</v>
+        <v>3.337227979168125</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684123229331691</v>
+        <v>4.654490752903994</v>
       </c>
       <c r="K8" t="n">
-        <v>12.1834596647409</v>
+        <v>18.71115433932723</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70264506401227</v>
+        <v>42.19103372439235</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81243283093336</v>
+        <v>99.88891108863785</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.71784850219366</v>
+        <v>79.13623152733271</v>
       </c>
       <c r="C9" t="n">
-        <v>41.70272148944194</v>
+        <v>37.35096473988277</v>
       </c>
       <c r="D9" t="n">
-        <v>1.888460836632497</v>
+        <v>1.739298620679528</v>
       </c>
       <c r="E9" t="n">
-        <v>9.923985705411297</v>
+        <v>8.256512669429583</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508317844718766</v>
+        <v>0.745591912442281</v>
       </c>
       <c r="G9" t="n">
-        <v>29.21579010882571</v>
+        <v>26.65336605147269</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53826208570631</v>
+        <v>34.29722797234493</v>
       </c>
       <c r="I9" t="n">
-        <v>4.707819328196732</v>
+        <v>2.784284848199453</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692698652949227</v>
+        <v>4.659949452764256</v>
       </c>
       <c r="K9" t="n">
-        <v>14.28215149780635</v>
+        <v>20.86376847266727</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85848647031497</v>
+        <v>41.69256601025084</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84335945756327</v>
+        <v>99.90729922280089</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.50398198378943</v>
+        <v>84.80325239660644</v>
       </c>
       <c r="C10" t="n">
-        <v>40.21906571252002</v>
+        <v>41.19644963592372</v>
       </c>
       <c r="D10" t="n">
-        <v>1.78936253850351</v>
+        <v>1.741279015549292</v>
       </c>
       <c r="E10" t="n">
-        <v>10.05810703698353</v>
+        <v>10.41031424333441</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520094810605161</v>
+        <v>0.7464408560226312</v>
       </c>
       <c r="G10" t="n">
-        <v>27.68267116766669</v>
+        <v>28.34532249635874</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59243612878372</v>
+        <v>35.99788784788589</v>
       </c>
       <c r="I10" t="n">
-        <v>3.929336374163246</v>
+        <v>2.896752587314032</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700059256628225</v>
+        <v>4.665255350141445</v>
       </c>
       <c r="K10" t="n">
-        <v>16.49601801621058</v>
+        <v>15.19674760339357</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15414351215281</v>
+        <v>43.51035415911697</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8692272408834</v>
+        <v>99.90355139843425</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.04114371103145</v>
+        <v>84.27855733607174</v>
       </c>
       <c r="C11" t="n">
-        <v>38.36505311453451</v>
+        <v>40.99150504883992</v>
       </c>
       <c r="D11" t="n">
-        <v>1.680143108907689</v>
+        <v>1.708743257036975</v>
       </c>
       <c r="E11" t="n">
-        <v>9.990655678865034</v>
+        <v>10.6944588694436</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530236721141623</v>
+        <v>0.7471725050874662</v>
       </c>
       <c r="G11" t="n">
-        <v>25.99297135023905</v>
+        <v>27.88130961712834</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63908891725145</v>
+        <v>36.09879120840946</v>
       </c>
       <c r="I11" t="n">
-        <v>3.278863032940546</v>
+        <v>2.478253722169234</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706397950713513</v>
+        <v>4.669828156796664</v>
       </c>
       <c r="K11" t="n">
-        <v>18.95885628896854</v>
+        <v>15.72144266392828</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56694236388132</v>
+        <v>43.20452472198988</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89085176738438</v>
+        <v>99.91747243475807</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.53999537158968</v>
+        <v>82.10655835015017</v>
       </c>
       <c r="C12" t="n">
-        <v>36.37104311414814</v>
+        <v>39.20388716863167</v>
       </c>
       <c r="D12" t="n">
-        <v>1.570390499309184</v>
+        <v>1.617970389601432</v>
       </c>
       <c r="E12" t="n">
-        <v>9.793958745625099</v>
+        <v>10.47083225209563</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538979358361497</v>
+        <v>0.7477994805973216</v>
       </c>
       <c r="G12" t="n">
-        <v>24.29502287086065</v>
+        <v>26.40018223805472</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67930504846287</v>
+        <v>36.12908281827057</v>
       </c>
       <c r="I12" t="n">
-        <v>2.735558172519816</v>
+        <v>2.066944417797229</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711862098975934</v>
+        <v>4.67374675373326</v>
       </c>
       <c r="K12" t="n">
-        <v>21.46000462841031</v>
+        <v>17.89344164984983</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07787272874875</v>
+        <v>42.83383080034715</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9089204713072</v>
+        <v>99.93115961882866</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.0220621948952</v>
+        <v>83.47173743776763</v>
       </c>
       <c r="C13" t="n">
-        <v>34.27527551000877</v>
+        <v>40.3076194367865</v>
       </c>
       <c r="D13" t="n">
-        <v>1.460964433672504</v>
+        <v>1.6192131567815</v>
       </c>
       <c r="E13" t="n">
-        <v>9.491826651310646</v>
+        <v>11.17499085451856</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546522472465347</v>
+        <v>0.7483738672843283</v>
       </c>
       <c r="G13" t="n">
-        <v>22.60212625152876</v>
+        <v>26.79600194342587</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71400337334057</v>
+        <v>36.532375316974</v>
       </c>
       <c r="I13" t="n">
-        <v>2.281912692505339</v>
+        <v>1.923445628256296</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71657654529084</v>
+        <v>4.677336670527052</v>
       </c>
       <c r="K13" t="n">
-        <v>23.97793780510482</v>
+        <v>16.52826256223239</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67079895787198</v>
+        <v>43.10005235569134</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92401227298556</v>
+        <v>99.93593435471023</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.09963542290399</v>
+        <v>81.24977731117693</v>
       </c>
       <c r="C14" t="n">
-        <v>38.64060870757494</v>
+        <v>38.3837649215663</v>
       </c>
       <c r="D14" t="n">
-        <v>1.462732633248296</v>
+        <v>1.52934214197715</v>
       </c>
       <c r="E14" t="n">
-        <v>11.92289296846187</v>
+        <v>10.82206754511652</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555655999282951</v>
+        <v>0.7488663143223726</v>
       </c>
       <c r="G14" t="n">
-        <v>24.54618408447208</v>
+        <v>25.30874631110273</v>
       </c>
       <c r="H14" t="n">
-        <v>36.6727201640896</v>
+        <v>36.55641445142808</v>
       </c>
       <c r="I14" t="n">
-        <v>3.017254973152006</v>
+        <v>1.603926082715244</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722284999551842</v>
+        <v>4.680414464514829</v>
       </c>
       <c r="K14" t="n">
-        <v>16.90036457709601</v>
+        <v>18.75022268882307</v>
       </c>
       <c r="L14" t="n">
-        <v>44.35857312814346</v>
+        <v>42.81258334438131</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89954641281442</v>
+        <v>99.94657095477068</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.33419619033387</v>
+        <v>80.24960220252142</v>
       </c>
       <c r="C15" t="n">
-        <v>38.34099924425598</v>
+        <v>37.59461837124002</v>
       </c>
       <c r="D15" t="n">
-        <v>1.434676078667855</v>
+        <v>1.487646586707981</v>
       </c>
       <c r="E15" t="n">
-        <v>12.11369115058444</v>
+        <v>10.75792034268134</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563355166567683</v>
+        <v>0.7492927233234281</v>
       </c>
       <c r="G15" t="n">
-        <v>24.07536574224491</v>
+        <v>24.62116532122545</v>
       </c>
       <c r="H15" t="n">
-        <v>36.71008944180107</v>
+        <v>36.5796594664931</v>
       </c>
       <c r="I15" t="n">
-        <v>2.516941281274031</v>
+        <v>1.370838241318677</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7270969791048</v>
+        <v>4.683079520771426</v>
       </c>
       <c r="K15" t="n">
-        <v>17.66580380966613</v>
+        <v>19.75039779747859</v>
       </c>
       <c r="L15" t="n">
-        <v>43.90938430793477</v>
+        <v>42.60931522721633</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91618736185688</v>
+        <v>99.95433139593493</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.89737076119172</v>
+        <v>77.64916851846654</v>
       </c>
       <c r="C16" t="n">
-        <v>36.29281823696657</v>
+        <v>35.20598549006647</v>
       </c>
       <c r="D16" t="n">
-        <v>1.342929684949301</v>
+        <v>1.383392282105816</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68891158517636</v>
+        <v>10.19449266960687</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569979356714431</v>
+        <v>0.7496603537467383</v>
       </c>
       <c r="G16" t="n">
-        <v>22.5357652587984</v>
+        <v>22.89571352911701</v>
       </c>
       <c r="H16" t="n">
-        <v>36.7422411267889</v>
+        <v>36.59760678571244</v>
       </c>
       <c r="I16" t="n">
-        <v>2.099288071860804</v>
+        <v>1.142925687260557</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731237097946518</v>
+        <v>4.685377210917115</v>
       </c>
       <c r="K16" t="n">
-        <v>20.10262923880826</v>
+        <v>22.35083148153346</v>
       </c>
       <c r="L16" t="n">
-        <v>43.53463748863422</v>
+        <v>42.40510418836343</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93008496440906</v>
+        <v>99.96192115996337</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.76328044788323</v>
+        <v>83.07068368310576</v>
       </c>
       <c r="C17" t="n">
-        <v>37.63407663371738</v>
+        <v>38.79411529205767</v>
       </c>
       <c r="D17" t="n">
-        <v>1.344083850230601</v>
+        <v>1.384098595525526</v>
       </c>
       <c r="E17" t="n">
-        <v>12.52993252242467</v>
+        <v>12.09207016184922</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576485287331346</v>
+        <v>0.7500431050277198</v>
       </c>
       <c r="G17" t="n">
-        <v>23.03475590129867</v>
+        <v>24.58771039590113</v>
       </c>
       <c r="H17" t="n">
-        <v>37.25344135956053</v>
+        <v>38.2965993768531</v>
       </c>
       <c r="I17" t="n">
-        <v>2.108114981053541</v>
+        <v>1.272392641525821</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735303304582089</v>
+        <v>4.687769406423248</v>
       </c>
       <c r="K17" t="n">
-        <v>18.23671955211677</v>
+        <v>16.92931631689425</v>
       </c>
       <c r="L17" t="n">
-        <v>44.05899365610024</v>
+        <v>44.23417694663834</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92978984193439</v>
+        <v>99.95760855559024</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.46414513426171</v>
+        <v>84.80744445930355</v>
       </c>
       <c r="C18" t="n">
-        <v>35.6600792364341</v>
+        <v>39.5452371681446</v>
       </c>
       <c r="D18" t="n">
-        <v>1.261287134829966</v>
+        <v>1.385298842808743</v>
       </c>
       <c r="E18" t="n">
-        <v>12.05108762847772</v>
+        <v>12.71309271812383</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582072671343375</v>
+        <v>0.7506935190964973</v>
       </c>
       <c r="G18" t="n">
-        <v>21.61579522532916</v>
+        <v>24.7304444886921</v>
       </c>
       <c r="H18" t="n">
-        <v>37.28091442586391</v>
+        <v>38.32980899754565</v>
       </c>
       <c r="I18" t="n">
-        <v>1.758058033037021</v>
+        <v>2.206271398683629</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738795419589607</v>
+        <v>4.691834494353108</v>
       </c>
       <c r="K18" t="n">
-        <v>20.53585486573829</v>
+        <v>15.19255554069643</v>
       </c>
       <c r="L18" t="n">
-        <v>43.7455071483539</v>
+        <v>45.18872862961439</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94144125052628</v>
+        <v>99.92652133845542</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.59690848223825</v>
+        <v>81.81003127355946</v>
       </c>
       <c r="C19" t="n">
-        <v>35.06331533055841</v>
+        <v>36.88854296612756</v>
       </c>
       <c r="D19" t="n">
-        <v>1.230735149503989</v>
+        <v>1.279318302332207</v>
       </c>
       <c r="E19" t="n">
-        <v>12.00350232047151</v>
+        <v>12.04714990144111</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586786601144122</v>
+        <v>0.7512562982495162</v>
       </c>
       <c r="G19" t="n">
-        <v>21.09219878142932</v>
+        <v>22.83847302943462</v>
       </c>
       <c r="H19" t="n">
-        <v>37.30409273358119</v>
+        <v>38.35854404972644</v>
       </c>
       <c r="I19" t="n">
-        <v>1.465959211422755</v>
+        <v>1.839937828316089</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741741625715075</v>
+        <v>4.695351864059476</v>
       </c>
       <c r="K19" t="n">
-        <v>21.40309151776176</v>
+        <v>18.18996872644054</v>
       </c>
       <c r="L19" t="n">
-        <v>43.48475820631771</v>
+        <v>44.86020299080179</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95116505463787</v>
+        <v>99.93871468336989</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.1058218574824</v>
+        <v>78.61325458151393</v>
       </c>
       <c r="C20" t="n">
-        <v>32.79763373279431</v>
+        <v>33.97496776001141</v>
       </c>
       <c r="D20" t="n">
-        <v>1.142031138757569</v>
+        <v>1.166992489785201</v>
       </c>
       <c r="E20" t="n">
-        <v>11.34207628502921</v>
+        <v>11.24510762455406</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590848151196027</v>
+        <v>0.7517450354985213</v>
       </c>
       <c r="G20" t="n">
-        <v>19.57199955080885</v>
+        <v>20.83322536301144</v>
       </c>
       <c r="H20" t="n">
-        <v>37.32406330185255</v>
+        <v>38.38349858167297</v>
       </c>
       <c r="I20" t="n">
-        <v>1.222286671417104</v>
+        <v>1.534279015125982</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744280094497515</v>
+        <v>4.698406471865757</v>
       </c>
       <c r="K20" t="n">
-        <v>23.89417814251761</v>
+        <v>21.38674541848605</v>
       </c>
       <c r="L20" t="n">
-        <v>43.26746703548189</v>
+        <v>44.58717743738266</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95927891079381</v>
+        <v>99.94889061588012</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.02690915890462</v>
+        <v>75.50624889954476</v>
       </c>
       <c r="C21" t="n">
-        <v>36.46802560330845</v>
+        <v>31.10315913853643</v>
       </c>
       <c r="D21" t="n">
-        <v>1.142844664850244</v>
+        <v>1.058526443754682</v>
       </c>
       <c r="E21" t="n">
-        <v>13.32395348011676</v>
+        <v>10.41314643475337</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596255493278881</v>
+        <v>0.7521695912422431</v>
       </c>
       <c r="G21" t="n">
-        <v>21.26757991378925</v>
+        <v>18.8968824979391</v>
       </c>
       <c r="H21" t="n">
-        <v>39.03228935072556</v>
+        <v>38.40517605743599</v>
       </c>
       <c r="I21" t="n">
-        <v>1.752956516795612</v>
+        <v>1.279287929155349</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747659683299299</v>
+        <v>4.701059945264019</v>
       </c>
       <c r="K21" t="n">
-        <v>17.97309084109538</v>
+        <v>24.49375110045522</v>
       </c>
       <c r="L21" t="n">
-        <v>45.50049326603655</v>
+        <v>44.36047089947705</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94160971044037</v>
+        <v>99.95738113846872</v>
       </c>
     </row>
   </sheetData>
